--- a/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplateError_region1.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplateError_region1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <r>
       <rPr>
@@ -389,6 +389,111 @@
     <t>保险费</t>
   </si>
   <si>
+    <t>错误信息</t>
+  </si>
+  <si>
+    <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.currency}</t>
+  </si>
+  <si>
+    <t>{.weightUnit}</t>
+  </si>
+  <si>
+    <t>{.priceBinary}</t>
+  </si>
+  <si>
+    <t>{.volumeSetting}</t>
+  </si>
+  <si>
+    <t>{.effectiveDate}</t>
+  </si>
+  <si>
+    <t>{.expireDate}</t>
+  </si>
+  <si>
+    <t>{.fromCountry}</t>
+  </si>
+  <si>
+    <t>{.toCountry}</t>
+  </si>
+  <si>
+    <t>{.region}</t>
+  </si>
+  <si>
+    <t>{.startWeight}</t>
+  </si>
+  <si>
+    <t>{.endWeight}</t>
+  </si>
+  <si>
+    <t>{.firstWeight}</t>
+  </si>
+  <si>
+    <t>{.firstWeightShippingCost}</t>
+  </si>
+  <si>
+    <t>{.additionalUnitWeight}</t>
+  </si>
+  <si>
+    <t>{.additionalPrice}</t>
+  </si>
+  <si>
+    <t>{.registrationCost}</t>
+  </si>
+  <si>
+    <t>{.operatingCost}</t>
+  </si>
+  <si>
+    <t>{.minCost}</t>
+  </si>
+  <si>
+    <t>{.discountRate}</t>
+  </si>
+  <si>
+    <t>{.signatureCost}</t>
+  </si>
+  <si>
+    <t>{.fuelSurchargeRate}</t>
+  </si>
+  <si>
+    <t>{.premiumCost}</t>
+  </si>
+  <si>
+    <t>{.errorMsg}</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>国家</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>分区</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -407,30 +512,14 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>分区</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>城市名称</t>
     </r>
+  </si>
+  <si>
+    <t>{.country}</t>
+  </si>
+  <si>
+    <t>{.city}</t>
   </si>
 </sst>
 </file>
@@ -1057,8 +1146,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1414,7 +1509,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="20.875" customWidth="1"/>
@@ -1436,98 +1531,158 @@
     <col min="19" max="19" width="11.375" customWidth="1"/>
     <col min="20" max="20" width="11.875" customWidth="1"/>
     <col min="22" max="22" width="14.5" customWidth="1"/>
+    <col min="24" max="24" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="20.25" customHeight="1" spans="1:23">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="4" customFormat="1" ht="20.25" customHeight="1" spans="1:24">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="6:6">
-      <c r="F2" s="3"/>
+    <row r="2" spans="1:24">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W2" t="s">
+        <v>46</v>
+      </c>
+      <c r="X2" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
-      <formula1>"CNY,JPY,GBP,CAD,USD,EUR,KRW,AUD"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
-      <formula1>"kg,g"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
-      <formula1>"0.01  保留两位小数四金五入,0.1  保留一位小数四舍五入,0  向下取整，小数舍弃,0.5  0.5进制,1  向上取整，小数进1,2  保留整数，四舍五入"</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 G$1:G$1048576">
-      <formula1>32874</formula1>
-      <formula2>398117</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1537,18 +1692,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="11.875" customWidth="1"/>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="18.375" customWidth="1"/>
+    <col min="3" max="3" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
+    <row r="1" s="1" customFormat="1" ht="26" customHeight="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplateError_region1.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplateError_region1.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="分区城市" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -149,6 +149,9 @@
     </r>
   </si>
   <si>
+    <t>失效日期</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -167,7 +170,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>失效日期</t>
+      <t>起始地</t>
     </r>
   </si>
   <si>
@@ -189,7 +192,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>起始地</t>
+      <t>目的地</t>
     </r>
   </si>
   <si>
@@ -206,12 +209,33 @@
     <r>
       <rPr>
         <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>城市分区</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>目的地</t>
+      <t>开始重量</t>
     </r>
   </si>
   <si>
@@ -228,11 +252,12 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>城市分区</t>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>结束重量</t>
     </r>
   </si>
   <si>
@@ -254,7 +279,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>开始重量</t>
+      <t>首重</t>
     </r>
   </si>
   <si>
@@ -276,7 +301,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>结束重量</t>
+      <t>首重运费</t>
     </r>
   </si>
   <si>
@@ -298,7 +323,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>首重</t>
+      <t>续重单位重量</t>
     </r>
   </si>
   <si>
@@ -320,8 +345,104 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>首重运费</t>
-    </r>
+      <t>续重单价</t>
+    </r>
+  </si>
+  <si>
+    <t>挂号费</t>
+  </si>
+  <si>
+    <t>操作费</t>
+  </si>
+  <si>
+    <t>最低收费</t>
+  </si>
+  <si>
+    <t>折扣费率</t>
+  </si>
+  <si>
+    <t>签名费</t>
+  </si>
+  <si>
+    <t>燃油附加费率</t>
+  </si>
+  <si>
+    <t>保险费</t>
+  </si>
+  <si>
+    <t>错误信息</t>
+  </si>
+  <si>
+    <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.currency}</t>
+  </si>
+  <si>
+    <t>{.weightUnit}</t>
+  </si>
+  <si>
+    <t>{.priceBinary}</t>
+  </si>
+  <si>
+    <t>{.volumeSetting}</t>
+  </si>
+  <si>
+    <t>{.effectiveDate}</t>
+  </si>
+  <si>
+    <t>{.expireDate}</t>
+  </si>
+  <si>
+    <t>{.fromCountry}</t>
+  </si>
+  <si>
+    <t>{.toCountry}</t>
+  </si>
+  <si>
+    <t>{.region}</t>
+  </si>
+  <si>
+    <t>{.startWeight}</t>
+  </si>
+  <si>
+    <t>{.endWeight}</t>
+  </si>
+  <si>
+    <t>{.firstWeight}</t>
+  </si>
+  <si>
+    <t>{.firstWeightShippingCost}</t>
+  </si>
+  <si>
+    <t>{.additionalUnitWeight}</t>
+  </si>
+  <si>
+    <t>{.additionalPrice}</t>
+  </si>
+  <si>
+    <t>{.registrationCost}</t>
+  </si>
+  <si>
+    <t>{.operatingCost}</t>
+  </si>
+  <si>
+    <t>{.minCost}</t>
+  </si>
+  <si>
+    <t>{.discountRate}</t>
+  </si>
+  <si>
+    <t>{.signatureCost}</t>
+  </si>
+  <si>
+    <t>{.fuelSurchargeRate}</t>
+  </si>
+  <si>
+    <t>{.premiumCost}</t>
+  </si>
+  <si>
+    <t>{.errorMsg}</t>
   </si>
   <si>
     <r>
@@ -342,7 +463,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>续重单位重量</t>
+      <t>国家</t>
     </r>
   </si>
   <si>
@@ -354,132 +475,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>续重单价</t>
-    </r>
-  </si>
-  <si>
-    <t>挂号费</t>
-  </si>
-  <si>
-    <t>操作费</t>
-  </si>
-  <si>
-    <t>最低收费</t>
-  </si>
-  <si>
-    <t>折扣费率</t>
-  </si>
-  <si>
-    <t>签名费</t>
-  </si>
-  <si>
-    <t>燃油附加费率</t>
-  </si>
-  <si>
-    <t>保险费</t>
-  </si>
-  <si>
-    <t>错误信息</t>
-  </si>
-  <si>
-    <t>{.name}</t>
-  </si>
-  <si>
-    <t>{.currency}</t>
-  </si>
-  <si>
-    <t>{.weightUnit}</t>
-  </si>
-  <si>
-    <t>{.priceBinary}</t>
-  </si>
-  <si>
-    <t>{.volumeSetting}</t>
-  </si>
-  <si>
-    <t>{.effectiveDate}</t>
-  </si>
-  <si>
-    <t>{.expireDate}</t>
-  </si>
-  <si>
-    <t>{.fromCountry}</t>
-  </si>
-  <si>
-    <t>{.toCountry}</t>
-  </si>
-  <si>
-    <t>{.region}</t>
-  </si>
-  <si>
-    <t>{.startWeight}</t>
-  </si>
-  <si>
-    <t>{.endWeight}</t>
-  </si>
-  <si>
-    <t>{.firstWeight}</t>
-  </si>
-  <si>
-    <t>{.firstWeightShippingCost}</t>
-  </si>
-  <si>
-    <t>{.additionalUnitWeight}</t>
-  </si>
-  <si>
-    <t>{.additionalPrice}</t>
-  </si>
-  <si>
-    <t>{.registrationCost}</t>
-  </si>
-  <si>
-    <t>{.operatingCost}</t>
-  </si>
-  <si>
-    <t>{.minCost}</t>
-  </si>
-  <si>
-    <t>{.discountRate}</t>
-  </si>
-  <si>
-    <t>{.signatureCost}</t>
-  </si>
-  <si>
-    <t>{.fuelSurchargeRate}</t>
-  </si>
-  <si>
-    <t>{.premiumCost}</t>
-  </si>
-  <si>
-    <t>{.errorMsg}</t>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>国家</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>*</t>
     </r>
     <r>
@@ -1146,18 +1141,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1534,77 +1523,77 @@
     <col min="24" max="24" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="20.25" customHeight="1" spans="1:24">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:24">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1624,7 +1613,7 @@
       <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G2" t="s">
@@ -1704,10 +1693,10 @@
       <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>50</v>
       </c>
     </row>
